--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_2.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01920497686385941</v>
+        <v>0.008740615205633918</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008412105359976642</v>
+        <v>0.008402251151435237</v>
       </c>
       <c r="C2" t="n">
-        <v>12625956</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12625956</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9091921</v>
+        <v>4824430</v>
       </c>
       <c r="L2" t="n">
-        <v>5217340</v>
+        <v>2904669</v>
       </c>
       <c r="M2" t="n">
-        <v>1224223</v>
+        <v>708991</v>
       </c>
       <c r="N2" t="n">
-        <v>44278</v>
+        <v>23805</v>
       </c>
       <c r="O2" t="n">
-        <v>723770</v>
+        <v>400578</v>
       </c>
       <c r="P2" t="n">
-        <v>283425</v>
+        <v>148385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999915957450867</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8948843479156494</v>
+        <v>0.9363389015197754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7789968252182007</v>
+        <v>0.869678795337677</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7185575366020203</v>
+        <v>0.8298290371894836</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2169947773218155</v>
+        <v>0.2467095106840134</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7697437405586243</v>
+        <v>0.8526328802108765</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8649048805236816</v>
+        <v>0.9479107260704041</v>
       </c>
       <c r="X2" t="n">
-        <v>12625956</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12625956</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9646677</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5928834</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1598278</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>117921</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917692</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567450881004333</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112150073051453</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582985401153564</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627530455589294</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020664095878601</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,425 +786,425 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004435287647227586</v>
+        <v>0.001907401200561638</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002017379093236049</v>
+        <v>0.002013410135496696</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9091921</v>
+        <v>4824430</v>
       </c>
       <c r="E3" t="n">
-        <v>970493</v>
+        <v>243591</v>
       </c>
       <c r="F3" t="n">
-        <v>9055</v>
+        <v>1031</v>
       </c>
       <c r="G3" t="n">
-        <v>1092</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
-        <v>426</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>20033138</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>21518201</v>
+        <v>11018683</v>
       </c>
       <c r="L3" t="n">
-        <v>24664359</v>
+        <v>12705873</v>
       </c>
       <c r="M3" t="n">
-        <v>30316534</v>
+        <v>15336899</v>
       </c>
       <c r="N3" t="n">
-        <v>32321358</v>
+        <v>16254050</v>
       </c>
       <c r="O3" t="n">
-        <v>31424938</v>
+        <v>15837572</v>
       </c>
       <c r="P3" t="n">
-        <v>32228385</v>
+        <v>16214564</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9025998711585999</v>
+        <v>0.9516941905021667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8008602261543274</v>
+        <v>0.8869589567184448</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6570659875869751</v>
+        <v>0.7593267560005188</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2486564218997955</v>
+        <v>0.2666778564453125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7111415266990662</v>
+        <v>0.7866919040679932</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7332264184951782</v>
+        <v>0.7677124738693237</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9646677</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>395630</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17032</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13547</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20033244</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22150033</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25566849</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30532165</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32421126</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31541812</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32246147</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576732516288757</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100743532180786</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578290939331055</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66222083568573</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016799926757812</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05328033408496902</v>
+        <v>0.03436971891502708</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03184710126109398</v>
+        <v>0.03181825301110282</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1007214</v>
+        <v>301249</v>
       </c>
       <c r="E4" t="n">
-        <v>5217340</v>
+        <v>2904669</v>
       </c>
       <c r="F4" t="n">
-        <v>268534</v>
+        <v>67532</v>
       </c>
       <c r="G4" t="n">
-        <v>9025</v>
+        <v>784</v>
       </c>
       <c r="H4" t="n">
-        <v>11727</v>
+        <v>602</v>
       </c>
       <c r="I4" t="n">
-        <v>829</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>1067963</v>
+        <v>328010</v>
       </c>
       <c r="L4" t="n">
-        <v>1480171</v>
+        <v>435264</v>
       </c>
       <c r="M4" t="n">
-        <v>479500</v>
+        <v>145391</v>
       </c>
       <c r="N4" t="n">
-        <v>159773</v>
+        <v>72685</v>
       </c>
       <c r="O4" t="n">
-        <v>216504</v>
+        <v>69235</v>
       </c>
       <c r="P4" t="n">
-        <v>44270</v>
+        <v>8154</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999957680702209</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8987255692481995</v>
+        <v>0.9439540505409241</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7897772192955017</v>
+        <v>0.8782338500022888</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6864374279975891</v>
+        <v>0.7930139899253845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2317491918802261</v>
+        <v>0.2563053369522095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392830848693848</v>
+        <v>0.8183361887931824</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7936408519744873</v>
+        <v>0.8483482003211975</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>407180</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5928834</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>165287</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>10949</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>436131</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>577681</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>263869</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60005</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99630</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572089314460754</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106443524360657</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580637574195862</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624868512153625</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018731117248535</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>37953</v>
+        <v>17588</v>
       </c>
       <c r="E5" t="n">
-        <v>452419</v>
+        <v>171758</v>
       </c>
       <c r="F5" t="n">
-        <v>1224223</v>
+        <v>708991</v>
       </c>
       <c r="G5" t="n">
-        <v>51770</v>
+        <v>15492</v>
       </c>
       <c r="H5" t="n">
-        <v>91309</v>
+        <v>19463</v>
       </c>
       <c r="I5" t="n">
-        <v>5490</v>
+        <v>418</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>981115</v>
+        <v>244877</v>
       </c>
       <c r="L5" t="n">
-        <v>1297330</v>
+        <v>370194</v>
       </c>
       <c r="M5" t="n">
-        <v>638943</v>
+        <v>224719</v>
       </c>
       <c r="N5" t="n">
-        <v>133791</v>
+        <v>65460</v>
       </c>
       <c r="O5" t="n">
-        <v>293988</v>
+        <v>108615</v>
       </c>
       <c r="P5" t="n">
-        <v>103120</v>
+        <v>44897</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999967813491821</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.937258780002594</v>
+        <v>0.9651018977165222</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9149550199508667</v>
+        <v>0.9509345889091492</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9657540917396545</v>
+        <v>0.9774543046951294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9910113215446472</v>
+        <v>0.9915847182273865</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9843690991401672</v>
+        <v>0.9891660809516907</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9954870343208313</v>
+        <v>0.9967683553695679</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15974</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>169599</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1598278</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19854</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58195</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>426359</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>585836</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>264888</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60148</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100066</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735912084579468</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643740057945251</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838098883628845</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963210225105286</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938854575157166</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983761310577393</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>22731</v>
+        <v>9148</v>
       </c>
       <c r="E6" t="n">
-        <v>37475</v>
+        <v>18727</v>
       </c>
       <c r="F6" t="n">
-        <v>54736</v>
+        <v>31706</v>
       </c>
       <c r="G6" t="n">
-        <v>44278</v>
+        <v>23805</v>
       </c>
       <c r="H6" t="n">
-        <v>17589</v>
+        <v>5725</v>
       </c>
       <c r="I6" t="n">
-        <v>1252</v>
+        <v>150</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12866</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10669</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21709</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>117921</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13942</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>18963</v>
+        <v>1090</v>
       </c>
       <c r="F7" t="n">
-        <v>143175</v>
+        <v>44669</v>
       </c>
       <c r="G7" t="n">
-        <v>95118</v>
+        <v>55288</v>
       </c>
       <c r="H7" t="n">
-        <v>723770</v>
+        <v>400578</v>
       </c>
       <c r="I7" t="n">
-        <v>36654</v>
+        <v>7557</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1621</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59181</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15125</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917692</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>821</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>4000</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>2768</v>
+        <v>903</v>
       </c>
       <c r="H8" t="n">
-        <v>95453</v>
+        <v>43413</v>
       </c>
       <c r="I8" t="n">
-        <v>283425</v>
+        <v>148385</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
